--- a/artfynd/A 25279-2026 artfynd.xlsx
+++ b/artfynd/A 25279-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129661747</v>
+        <v>129661754</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741089</v>
+        <v>741066</v>
       </c>
       <c r="R2" t="n">
-        <v>7125802</v>
+        <v>7125531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129661759</v>
+        <v>129661755</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741109</v>
+        <v>741069</v>
       </c>
       <c r="R3" t="n">
-        <v>7125615</v>
+        <v>7125541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129661775</v>
+        <v>129661745</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740939</v>
+        <v>741090</v>
       </c>
       <c r="R4" t="n">
-        <v>7125650</v>
+        <v>7125500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661760</v>
+        <v>129661746</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741074</v>
+        <v>741066</v>
       </c>
       <c r="R5" t="n">
-        <v>7125538</v>
+        <v>7125531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661768</v>
+        <v>129661752</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741118</v>
+        <v>741091</v>
       </c>
       <c r="R6" t="n">
-        <v>7125616</v>
+        <v>7125499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661750</v>
+        <v>129661753</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,38 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740939</v>
+        <v>741071</v>
       </c>
       <c r="R7" t="n">
-        <v>7125650</v>
+        <v>7125530</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661755</v>
+        <v>129661772</v>
       </c>
       <c r="B8" t="n">
-        <v>91904</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741069</v>
+        <v>741126</v>
       </c>
       <c r="R8" t="n">
-        <v>7125541</v>
+        <v>7125873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661756</v>
+        <v>129661775</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741166</v>
+        <v>740939</v>
       </c>
       <c r="R9" t="n">
-        <v>7125623</v>
+        <v>7125650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B10" t="n">
-        <v>91904</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R10" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661751</v>
+        <v>129661767</v>
       </c>
       <c r="B11" t="n">
-        <v>80097</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741116</v>
+        <v>741196</v>
       </c>
       <c r="R11" t="n">
-        <v>7125615</v>
+        <v>7125593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661745</v>
+        <v>129661768</v>
       </c>
       <c r="B12" t="n">
-        <v>91606</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741090</v>
+        <v>741118</v>
       </c>
       <c r="R12" t="n">
-        <v>7125500</v>
+        <v>7125616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661753</v>
+        <v>129661747</v>
       </c>
       <c r="B13" t="n">
-        <v>92059</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741071</v>
+        <v>741089</v>
       </c>
       <c r="R13" t="n">
-        <v>7125530</v>
+        <v>7125802</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,27 +1839,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129661757</v>
+        <v>129661750</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1887,16 +1868,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741092</v>
+        <v>740939</v>
       </c>
       <c r="R14" t="n">
-        <v>7125804</v>
+        <v>7125650</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1929,11 +1914,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1960,10 +1940,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129661746</v>
+        <v>129661756</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1951,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741066</v>
+        <v>741166</v>
       </c>
       <c r="R15" t="n">
-        <v>7125531</v>
+        <v>7125623</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2031,6 +2011,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2057,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129661772</v>
+        <v>129661757</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2092,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741126</v>
+        <v>741092</v>
       </c>
       <c r="R16" t="n">
-        <v>7125873</v>
+        <v>7125804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,6 +2115,11 @@
           <t>2025-11-11</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2151,6 +2141,312 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129661759</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högkläppen, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>741109</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7125615</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129661760</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högkläppen, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>741074</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7125538</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129661761</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högkläppen, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>741173</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7125642</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25279-2026 artfynd.xlsx
+++ b/artfynd/A 25279-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661754</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661745</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661746</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661753</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661772</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661775</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661751</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661768</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661747</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661750</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661756</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661757</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661759</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2345,6 +2430,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661760</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2447,8 +2537,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661761</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>